--- a/artfynd/A 36298-2025 artfynd.xlsx
+++ b/artfynd/A 36298-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150966</v>
+        <v>121150952</v>
       </c>
       <c r="B2" t="n">
-        <v>97058</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>766314</v>
+        <v>766246</v>
       </c>
       <c r="R2" t="n">
-        <v>7445889</v>
+        <v>7445850</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150950</v>
+        <v>121150951</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>766295</v>
+        <v>766274</v>
       </c>
       <c r="R3" t="n">
-        <v>7445908</v>
+        <v>7445872</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150969</v>
+        <v>121150950</v>
       </c>
       <c r="B4" t="n">
-        <v>97058</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>766396</v>
+        <v>766295</v>
       </c>
       <c r="R4" t="n">
-        <v>7445745</v>
+        <v>7445908</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,42 +993,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150964</v>
+        <v>121150953</v>
       </c>
       <c r="B5" t="n">
-        <v>97058</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>766422</v>
+        <v>766193</v>
       </c>
       <c r="R5" t="n">
-        <v>7446071</v>
+        <v>7445754</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,19 +1099,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150953</v>
+        <v>121150967</v>
       </c>
       <c r="B6" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1154,7 +1129,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>766193</v>
+        <v>766325</v>
       </c>
       <c r="R6" t="n">
-        <v>7445754</v>
+        <v>7445882</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,42 +1205,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150954</v>
+        <v>121150968</v>
       </c>
       <c r="B7" t="n">
-        <v>97058</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>766176</v>
+        <v>766346</v>
       </c>
       <c r="R7" t="n">
-        <v>7445755</v>
+        <v>7445873</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121150949</v>
+        <v>121150955</v>
       </c>
       <c r="B8" t="n">
-        <v>97058</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,26 +1322,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1385,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>766338</v>
+        <v>766196</v>
       </c>
       <c r="R8" t="n">
-        <v>7445821</v>
+        <v>7445929</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,37 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121150951</v>
+        <v>121150956</v>
       </c>
       <c r="B9" t="n">
-        <v>91981</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>766274</v>
+        <v>766198</v>
       </c>
       <c r="R9" t="n">
-        <v>7445872</v>
+        <v>7445978</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,15 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121150968</v>
+        <v>121150960</v>
       </c>
       <c r="B10" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>766346</v>
+        <v>766218</v>
       </c>
       <c r="R10" t="n">
-        <v>7445873</v>
+        <v>7446024</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1674,15 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121150955</v>
+        <v>121150961</v>
       </c>
       <c r="B11" t="n">
-        <v>79723</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>766196</v>
+        <v>766225</v>
       </c>
       <c r="R11" t="n">
-        <v>7445929</v>
+        <v>7446057</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121150967</v>
+        <v>121150949</v>
       </c>
       <c r="B12" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,26 +1746,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1829,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>766325</v>
+        <v>766338</v>
       </c>
       <c r="R12" t="n">
-        <v>7445882</v>
+        <v>7445821</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1896,15 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121150963</v>
+        <v>121150954</v>
       </c>
       <c r="B13" t="n">
-        <v>97058</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,7 +1871,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1940,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>766353</v>
+        <v>766176</v>
       </c>
       <c r="R13" t="n">
-        <v>7446111</v>
+        <v>7445755</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2007,15 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121150965</v>
+        <v>121150963</v>
       </c>
       <c r="B14" t="n">
-        <v>97058</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +1977,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2051,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>766377</v>
+        <v>766353</v>
       </c>
       <c r="R14" t="n">
-        <v>7445984</v>
+        <v>7446111</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2118,37 +2053,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121150952</v>
+        <v>121150964</v>
       </c>
       <c r="B15" t="n">
-        <v>78689</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2162,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>766246</v>
+        <v>766422</v>
       </c>
       <c r="R15" t="n">
-        <v>7445850</v>
+        <v>7446071</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2226,6 +2156,324 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121150965</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Leipojärvi, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>766377</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7445984</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121150966</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Leipojärvi, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>766314</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7445889</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121150969</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Leipojärvi, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>766396</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7445745</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
